--- a/Mayfair Docs/Filled - Joes Jyoti Services/Vendor Registration Form - Joes Jyoti Services.xlsx
+++ b/Mayfair Docs/Filled - Joes Jyoti Services/Vendor Registration Form - Joes Jyoti Services.xlsx
@@ -613,7 +613,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2322,13 +2322,21 @@
       <c r="A32" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="9"/>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:2" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="22"/>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>919020019694374</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
@@ -2340,13 +2348,21 @@
       <c r="A35" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>UTIB0000381</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Axis Bank Ltd, Chandrasekharpur, Bhubaneswar, Odisha - 751016</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">

--- a/Mayfair Docs/Filled - Joes Jyoti Services/Vendor Registration Form - Joes Jyoti Services.xlsx
+++ b/Mayfair Docs/Filled - Joes Jyoti Services/Vendor Registration Form - Joes Jyoti Services.xlsx
@@ -2430,7 +2430,11 @@
       <c r="A44" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B44" s="9"/>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>UDYAM-OD-19-0057563</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
@@ -2458,13 +2462,21 @@
       <c r="A48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="9"/>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>Yes - Udyam Registration No. UDYAM-OD-19-0057563 (Micro enterprise)</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B49" s="9"/>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
